--- a/data/trans_dic/P34B04_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P34B04_R-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza algún entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares, 3 veces por semana o más</t>
+          <t>Población que realiza algún entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,46; 13,42</t>
+          <t>6,59; 13,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 13,63</t>
+          <t>6,35; 13,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,97; 16,68</t>
+          <t>5,24; 17,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,26</t>
+          <t>0,34; 4,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,96</t>
+          <t>0,67; 3,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 1,31</t>
+          <t>0,06; 1,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,86; 7,89</t>
+          <t>3,85; 7,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,0; 8,13</t>
+          <t>4,0; 7,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 9,15</t>
+          <t>2,74; 9,66</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,69; 9,45</t>
+          <t>4,84; 9,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,04; 8,21</t>
+          <t>4,06; 8,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,63; 13,36</t>
+          <t>4,43; 12,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,44</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,14</t>
+          <t>0,38; 2,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,9</t>
+          <t>0,0; 0,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,14</t>
+          <t>2,49; 5,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,64</t>
+          <t>2,19; 4,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 6,87</t>
+          <t>2,3; 6,96</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,0; 10,81</t>
+          <t>5,22; 10,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 7,52</t>
+          <t>2,93; 7,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,93</t>
+          <t>1,15; 5,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,73</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,85</t>
+          <t>0,79; 3,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 5,54</t>
+          <t>2,59; 5,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,87</t>
+          <t>1,47; 3,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,12</t>
+          <t>1,28; 4,21</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,5; 10,92</t>
+          <t>5,6; 10,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,97; 10,83</t>
+          <t>5,43; 11,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,13; 11,54</t>
+          <t>4,04; 10,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,71</t>
+          <t>0,83; 4,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,2</t>
+          <t>0,24; 2,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,35</t>
+          <t>1,07; 4,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,8</t>
+          <t>3,51; 6,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,84</t>
+          <t>2,85; 6,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 6,11</t>
+          <t>2,68; 6,23</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,3; 13,97</t>
+          <t>5,36; 13,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,64; 8,4</t>
+          <t>2,64; 8,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,06; 15,74</t>
+          <t>5,94; 15,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,29</t>
+          <t>0,4; 3,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,17</t>
+          <t>0,4; 2,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,4</t>
+          <t>2,63; 6,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,84</t>
+          <t>1,82; 5,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,33; 7,99</t>
+          <t>3,31; 8,37</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,07; 12,42</t>
+          <t>5,71; 13,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,63; 9,29</t>
+          <t>3,66; 9,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,25; 12,93</t>
+          <t>5,25; 13,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,21</t>
+          <t>0,34; 4,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,09; 5,09</t>
+          <t>1,37; 5,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,89</t>
+          <t>0,94; 4,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,25; 7,38</t>
+          <t>3,08; 7,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,86; 6,32</t>
+          <t>2,83; 6,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,49; 8,09</t>
+          <t>3,45; 7,94</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,69; 10,01</t>
+          <t>5,78; 10,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,4; 9,71</t>
+          <t>5,35; 9,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,84; 12,47</t>
+          <t>5,86; 12,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,35</t>
+          <t>0,14; 1,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,19</t>
+          <t>1,07; 3,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,71</t>
+          <t>1,22; 4,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,15</t>
+          <t>2,98; 5,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,54; 5,85</t>
+          <t>3,6; 5,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,21; 7,08</t>
+          <t>3,12; 7,23</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,32; 7,76</t>
+          <t>4,33; 7,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,59; 6,67</t>
+          <t>3,54; 6,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,07; 14,32</t>
+          <t>4,31; 14,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,01</t>
+          <t>0,12; 1,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,67</t>
+          <t>0,36; 1,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,22</t>
+          <t>0,6; 2,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,97</t>
+          <t>2,26; 4,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,75</t>
+          <t>2,07; 3,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,33; 7,81</t>
+          <t>3,8; 7,84</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,56; 8,35</t>
+          <t>6,55; 8,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,55; 7,22</t>
+          <t>5,51; 7,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,49; 9,71</t>
+          <t>6,44; 9,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,14</t>
+          <t>0,51; 1,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,67</t>
+          <t>0,95; 1,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,13</t>
+          <t>1,22; 2,15</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,57; 4,56</t>
+          <t>3,52; 4,55</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,33; 4,22</t>
+          <t>3,3; 4,27</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,06; 5,6</t>
+          <t>4,11; 5,64</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza algún entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares, 3 veces por semana o más</t>
+          <t>Población que realiza algún entrenamiento físico deportivo, como fútbol, baloncesto, ciclismo, natación de competición, judo, kárate o similares, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18957; 39385</t>
+          <t>19350; 39985</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19287; 40053</t>
+          <t>18645; 40221</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15480; 51943</t>
+          <t>16323; 54933</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>974; 12237</t>
+          <t>976; 12616</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2133; 11422</t>
+          <t>1928; 11329</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>173; 3808</t>
+          <t>167; 3862</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22415; 45804</t>
+          <t>22354; 43693</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23298; 47364</t>
+          <t>23299; 45395</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16408; 55028</t>
+          <t>16479; 58039</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23712; 47790</t>
+          <t>24443; 48864</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20291; 41250</t>
+          <t>20389; 42039</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23979; 69258</t>
+          <t>22948; 63228</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 7506</t>
+          <t>0; 7073</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1977; 11190</t>
+          <t>1979; 11724</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4639</t>
+          <t>0; 4722</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25935; 52844</t>
+          <t>25566; 51952</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24540; 47589</t>
+          <t>22420; 46606</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24291; 70942</t>
+          <t>23761; 71954</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16198; 35041</t>
+          <t>16914; 34953</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9203; 23943</t>
+          <t>9335; 24512</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3500; 18758</t>
+          <t>3624; 18798</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5888</t>
+          <t>0; 6876</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1939</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2885; 13428</t>
+          <t>2747; 13338</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17933; 36823</t>
+          <t>17250; 37511</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9387; 25322</t>
+          <t>9619; 25460</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8196; 27421</t>
+          <t>8513; 27975</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20578; 40849</t>
+          <t>20954; 40606</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18370; 40068</t>
+          <t>20089; 42248</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12921; 36070</t>
+          <t>12623; 34003</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3180; 14432</t>
+          <t>3211; 15613</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>941; 8527</t>
+          <t>934; 9369</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5166; 20694</t>
+          <t>5082; 19900</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26491; 51906</t>
+          <t>26760; 51258</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21964; 44243</t>
+          <t>21575; 45741</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20191; 48157</t>
+          <t>21131; 49089</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11272; 29705</t>
+          <t>11406; 28602</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5569; 17732</t>
+          <t>5581; 18252</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10830; 28135</t>
+          <t>10622; 27621</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 1978</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>873; 7189</t>
+          <t>872; 7014</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>810; 4518</t>
+          <t>836; 4791</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10398; 27670</t>
+          <t>11366; 28576</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7482; 20786</t>
+          <t>7844; 22363</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12888; 30911</t>
+          <t>12829; 32383</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13902; 34029</t>
+          <t>15632; 36833</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9541; 24437</t>
+          <t>9627; 24258</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14144; 34860</t>
+          <t>14144; 35647</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1741; 11786</t>
+          <t>957; 12294</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2989; 13913</t>
+          <t>3730; 14208</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2164; 12571</t>
+          <t>2404; 12169</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18029; 40874</t>
+          <t>17085; 40894</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15351; 33912</t>
+          <t>15197; 33726</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18398; 42591</t>
+          <t>18171; 41842</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>37641; 66275</t>
+          <t>38290; 67851</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>35442; 63746</t>
+          <t>35109; 63550</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36377; 77706</t>
+          <t>36533; 76810</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>958; 9381</t>
+          <t>966; 9622</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7177; 22069</t>
+          <t>7366; 22627</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10477; 39938</t>
+          <t>10357; 37858</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40696; 69867</t>
+          <t>40424; 70634</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>47771; 78897</t>
+          <t>48482; 80417</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>47178; 104121</t>
+          <t>45944; 106356</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>33656; 60491</t>
+          <t>33736; 60656</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>27957; 51926</t>
+          <t>27595; 51527</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>37815; 133018</t>
+          <t>40031; 134567</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>960; 8315</t>
+          <t>972; 9216</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2936; 13825</t>
+          <t>2944; 12994</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4085; 15849</t>
+          <t>4302; 15299</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>35798; 63628</t>
+          <t>36196; 64668</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>33557; 60135</t>
+          <t>33197; 58518</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>54723; 128230</t>
+          <t>62324; 128646</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>224671; 286021</t>
+          <t>224157; 285987</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>188244; 245235</t>
+          <t>187002; 245684</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>224525; 335682</t>
+          <t>222724; 334839</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18256; 40677</t>
+          <t>18211; 41107</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>32736; 59222</t>
+          <t>33511; 58462</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>45189; 77880</t>
+          <t>44685; 78759</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>249277; 318599</t>
+          <t>245520; 317842</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>230891; 292819</t>
+          <t>229156; 296573</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>288626; 398663</t>
+          <t>292302; 400992</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P34B04_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P34B04_R-Provincia-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,59; 13,62</t>
+          <t>6,43; 13,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,35; 13,69</t>
+          <t>6,35; 13,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,24; 17,64</t>
+          <t>4,8; 12,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,39</t>
+          <t>0,34; 4,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,92</t>
+          <t>0,88; 4,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 1,33</t>
+          <t>0,15; 1,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,85; 7,52</t>
+          <t>3,91; 7,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,0; 7,79</t>
+          <t>4,03; 7,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 9,66</t>
+          <t>2,5; 6,57</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,84; 9,67</t>
+          <t>4,88; 9,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,06; 8,36</t>
+          <t>3,96; 8,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,43; 12,2</t>
+          <t>3,95; 10,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,36</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,24</t>
+          <t>0,38; 2,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,92</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,06</t>
+          <t>2,59; 5,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,54</t>
+          <t>2,28; 4,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 6,96</t>
+          <t>2,13; 5,76</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -898,22 +898,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,22; 10,79</t>
+          <t>4,95; 10,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,93; 7,69</t>
+          <t>2,95; 7,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,95</t>
+          <t>1,08; 5,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,22 +923,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,82</t>
+          <t>0,74; 3,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,64</t>
+          <t>2,69; 5,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,89</t>
+          <t>1,45; 3,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,21</t>
+          <t>1,28; 3,76</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,6; 10,86</t>
+          <t>5,6; 11,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,43; 11,42</t>
+          <t>5,08; 10,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 10,88</t>
+          <t>5,52; 13,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,01</t>
+          <t>0,83; 3,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,42</t>
+          <t>0,24; 2,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,18</t>
+          <t>1,56; 5,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,51; 6,72</t>
+          <t>3,57; 6,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,85; 6,04</t>
+          <t>2,9; 6,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 6,23</t>
+          <t>3,81; 8,72</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -1118,17 +1118,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,36; 13,45</t>
+          <t>5,33; 13,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,64; 8,64</t>
+          <t>2,33; 8,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,94; 15,45</t>
+          <t>6,41; 16,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,21</t>
+          <t>0,4; 3,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,3</t>
+          <t>0,41; 2,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,63; 6,61</t>
+          <t>2,56; 6,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,2</t>
+          <t>1,75; 5,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,31; 8,37</t>
+          <t>3,67; 8,42</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,71; 13,44</t>
+          <t>5,29; 12,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,66; 9,22</t>
+          <t>3,31; 9,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,25; 13,22</t>
+          <t>4,62; 11,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,39</t>
+          <t>0,62; 4,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,37; 5,2</t>
+          <t>1,36; 5,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,73</t>
+          <t>0,9; 4,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,08; 7,38</t>
+          <t>3,33; 7,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,83; 6,29</t>
+          <t>2,84; 6,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,45; 7,94</t>
+          <t>3,25; 7,23</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1338,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,78; 10,25</t>
+          <t>5,66; 9,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,35; 9,68</t>
+          <t>5,37; 9,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,86; 12,33</t>
+          <t>6,44; 12,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1358,27 +1358,27 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,27</t>
+          <t>1,0; 3,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,46</t>
+          <t>2,43; 5,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,98; 5,21</t>
+          <t>3,0; 5,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,6; 5,97</t>
+          <t>3,51; 5,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,12; 7,23</t>
+          <t>4,77; 8,08</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,33; 7,79</t>
+          <t>4,39; 8,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,54; 6,62</t>
+          <t>3,51; 6,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,31; 14,49</t>
+          <t>10,84; 16,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,12</t>
+          <t>0,12; 1,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,57</t>
+          <t>0,36; 1,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,15</t>
+          <t>0,58; 2,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,03</t>
+          <t>2,3; 4,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,65</t>
+          <t>2,07; 3,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,8; 7,84</t>
+          <t>5,87; 8,73</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,55; 8,35</t>
+          <t>6,61; 8,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,51; 7,24</t>
+          <t>5,54; 7,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,44; 9,68</t>
+          <t>7,77; 10,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,16</t>
+          <t>0,5; 1,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,65</t>
+          <t>0,94; 1,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,15</t>
+          <t>1,44; 2,32</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,52; 4,55</t>
+          <t>3,57; 4,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,3; 4,27</t>
+          <t>3,3; 4,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,11; 5,64</t>
+          <t>4,66; 5,99</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29209</t>
+          <t>24426</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30475</t>
+          <t>25930</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19350; 39985</t>
+          <t>18869; 38807</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18645; 40221</t>
+          <t>18649; 40898</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16323; 54933</t>
+          <t>15314; 39722</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>976; 12616</t>
+          <t>982; 12692</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1928; 11329</t>
+          <t>2551; 12268</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>167; 3862</t>
+          <t>462; 4320</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22354; 43693</t>
+          <t>22736; 45789</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23299; 45395</t>
+          <t>23450; 46260</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16479; 58039</t>
+          <t>15862; 41694</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40668</t>
+          <t>36750</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>42186</t>
+          <t>38245</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24443; 48864</t>
+          <t>24660; 48960</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20389; 42039</t>
+          <t>19908; 41302</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22948; 63228</t>
+          <t>20948; 58231</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 7073</t>
+          <t>0; 7181</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1979; 11724</t>
+          <t>1966; 11242</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4722</t>
+          <t>0; 5138</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25566; 51952</t>
+          <t>26596; 52584</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22420; 46606</t>
+          <t>23346; 46367</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23761; 71954</t>
+          <t>22981; 62014</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8959</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>6346</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15436</t>
+          <t>14564</t>
         </is>
       </c>
     </row>
@@ -2187,22 +2187,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16914; 34953</t>
+          <t>16055; 34912</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9335; 24512</t>
+          <t>9411; 24625</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3624; 18798</t>
+          <t>3397; 17895</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 6876</t>
+          <t>0; 6355</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2212,22 +2212,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2747; 13338</t>
+          <t>2639; 13421</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17250; 37511</t>
+          <t>17895; 36388</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9619; 25460</t>
+          <t>9486; 24561</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8513; 27975</t>
+          <t>8578; 25312</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21543</t>
+          <t>32688</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11243</t>
+          <t>12654</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>32786</t>
+          <t>45342</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20954; 40606</t>
+          <t>20930; 42160</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20089; 42248</t>
+          <t>18802; 40345</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12623; 34003</t>
+          <t>20590; 51956</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3211; 15613</t>
+          <t>3218; 15498</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>934; 9369</t>
+          <t>934; 8573</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5082; 19900</t>
+          <t>6602; 21255</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26760; 51258</t>
+          <t>27201; 50487</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21575; 45741</t>
+          <t>21933; 45576</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21131; 49089</t>
+          <t>30258; 69365</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18088</t>
+          <t>22275</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20278</t>
+          <t>24883</t>
         </is>
       </c>
     </row>
@@ -2513,17 +2513,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11406; 28602</t>
+          <t>11329; 28990</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5581; 18252</t>
+          <t>4929; 17541</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10622; 27621</t>
+          <t>13178; 33592</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2533,27 +2533,27 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>872; 7014</t>
+          <t>874; 7108</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>836; 4791</t>
+          <t>922; 5435</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11366; 28576</t>
+          <t>11083; 28137</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7844; 22363</t>
+          <t>7521; 22068</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12829; 32383</t>
+          <t>15882; 36422</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22691</t>
+          <t>20898</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5874</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>28566</t>
+          <t>26623</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15632; 36833</t>
+          <t>14503; 34016</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9627; 24258</t>
+          <t>8713; 24346</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14144; 35647</t>
+          <t>12510; 32018</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>957; 12294</t>
+          <t>1734; 12678</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3730; 14208</t>
+          <t>3704; 14723</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2404; 12169</t>
+          <t>2385; 12120</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17085; 40894</t>
+          <t>18428; 41958</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15197; 33726</t>
+          <t>15256; 32938</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18171; 41842</t>
+          <t>17385; 38637</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>54275</t>
+          <t>62969</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23506</t>
+          <t>28366</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>77781</t>
+          <t>91335</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>38290; 67851</t>
+          <t>37445; 65909</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>35109; 63550</t>
+          <t>35275; 64697</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36533; 76810</t>
+          <t>46175; 87792</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>966; 9622</t>
+          <t>963; 9622</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7366; 22627</t>
+          <t>6926; 20816</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10357; 37858</t>
+          <t>18729; 41948</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40424; 70634</t>
+          <t>40670; 70627</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>48482; 80417</t>
+          <t>47312; 78603</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>45944; 106356</t>
+          <t>71034; 120267</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>91969</t>
+          <t>106922</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>9229</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>100158</t>
+          <t>116151</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>33736; 60656</t>
+          <t>34188; 62591</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>27595; 51527</t>
+          <t>27322; 50885</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>40031; 134567</t>
+          <t>86529; 130635</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>972; 9216</t>
+          <t>961; 8348</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2944; 12994</t>
+          <t>2940; 13838</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4302; 15299</t>
+          <t>4782; 18265</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>36196; 64668</t>
+          <t>36851; 64110</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>33197; 58518</t>
+          <t>33269; 59528</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>62324; 128646</t>
+          <t>95340; 141822</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>287401</t>
+          <t>315145</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>60263</t>
+          <t>67927</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>347664</t>
+          <t>383072</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>224157; 285987</t>
+          <t>226287; 287613</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>187002; 245684</t>
+          <t>187975; 243386</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>222724; 334839</t>
+          <t>274244; 360886</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18211; 41107</t>
+          <t>17891; 41586</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>33511; 58462</t>
+          <t>33294; 58771</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>44685; 78759</t>
+          <t>53587; 86655</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>245520; 317842</t>
+          <t>248887; 315449</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>229156; 296573</t>
+          <t>229198; 293767</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>292302; 400992</t>
+          <t>338497; 435086</t>
         </is>
       </c>
     </row>
